--- a/AAII_Financials/Yearly/IFBD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/IFBD_YR_FIN.xlsx
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>54800</v>
+        <v>51200</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
@@ -1279,7 +1279,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-57200</v>
+        <v>-53600</v>
       </c>
       <c r="E23" s="3">
         <v>-2100</v>
@@ -1405,7 +1405,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-57200</v>
+        <v>-53600</v>
       </c>
       <c r="E26" s="3">
         <v>-2100</v>
@@ -1447,7 +1447,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-57200</v>
+        <v>-52100</v>
       </c>
       <c r="E27" s="3">
         <v>-2100</v>
@@ -1699,7 +1699,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-57200</v>
+        <v>-52100</v>
       </c>
       <c r="E33" s="3">
         <v>-2100</v>
@@ -1783,7 +1783,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-57200</v>
+        <v>-52100</v>
       </c>
       <c r="E35" s="3">
         <v>-2100</v>
@@ -3138,7 +3138,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-83900</v>
+        <v>-78800</v>
       </c>
       <c r="E72" s="3">
         <v>-26700</v>
@@ -3306,7 +3306,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16000</v>
+        <v>17700</v>
       </c>
       <c r="E76" s="3">
         <v>64800</v>
@@ -3437,7 +3437,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-57200</v>
+        <v>-52100</v>
       </c>
       <c r="E81" s="3">
         <v>-2100</v>
